--- a/data/questions.xlsx
+++ b/data/questions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\P.SUJAYA RAGHAVI\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Adaptive-Competency-System\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F261CDB1-27C5-4921-A7DB-408715AEB178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB7A4DD-F525-40D9-8FCF-868FA60711D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{264EDFC2-168E-41CA-8368-4DE5FE7E006E}"/>
+    <workbookView xWindow="5772" yWindow="12" windowWidth="11712" windowHeight="13056" xr2:uid="{264EDFC2-168E-41CA-8368-4DE5FE7E006E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7498,7 +7498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
@@ -7530,7 +7530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
@@ -7562,7 +7562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="221.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="124.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
@@ -7594,7 +7594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -7626,7 +7626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="124.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
@@ -7658,7 +7658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="152.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="111" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
@@ -7722,7 +7722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="180" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="124.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
@@ -7754,7 +7754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="180" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="138.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>10</v>
       </c>
@@ -7786,7 +7786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="331.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" ht="221.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>10</v>
       </c>
@@ -7818,7 +7818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="166.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" ht="111" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>10</v>
       </c>
@@ -7850,7 +7850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="124.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>10</v>
       </c>
@@ -7882,7 +7882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="249" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" ht="180" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>10</v>
       </c>
@@ -7914,7 +7914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="193.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" ht="111" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>10</v>
       </c>
@@ -7946,7 +7946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="138.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" ht="97.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>10</v>
       </c>
@@ -7978,7 +7978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>10</v>
       </c>
@@ -8010,7 +8010,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="235.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" ht="180" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>10</v>
       </c>
@@ -8042,7 +8042,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="262.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" ht="193.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>10</v>
       </c>
@@ -8074,7 +8074,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="249" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" ht="166.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>10</v>
       </c>
@@ -8106,7 +8106,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="262.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" ht="166.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>10</v>
       </c>
@@ -8138,7 +8138,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="221.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" ht="166.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>10</v>
       </c>
@@ -8170,7 +8170,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="249" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" ht="180" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>10</v>
       </c>
@@ -8202,7 +8202,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="290.39999999999998" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" ht="193.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>10</v>
       </c>
@@ -8234,7 +8234,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="373.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" ht="262.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>10</v>
       </c>
@@ -8266,7 +8266,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="262.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" ht="180" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>10</v>
       </c>
@@ -8298,7 +8298,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="249" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" ht="180" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>10</v>
       </c>
@@ -8330,7 +8330,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="207.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" ht="180" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>10</v>
       </c>
@@ -8362,7 +8362,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="111" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>10</v>
       </c>
@@ -8394,7 +8394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="193.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" ht="138.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>10</v>
       </c>
@@ -8426,7 +8426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="152.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>10</v>
       </c>
@@ -8458,7 +8458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="235.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" ht="152.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>10</v>
       </c>
@@ -8490,7 +8490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="166.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" ht="111" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>10</v>
       </c>
@@ -8522,7 +8522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="207.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" ht="152.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>10</v>
       </c>
@@ -8554,7 +8554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="111" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>10</v>
       </c>
@@ -8586,7 +8586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="166.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10" ht="111" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>10</v>
       </c>
@@ -8618,7 +8618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="221.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" ht="152.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>10</v>
       </c>
@@ -8650,7 +8650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="180" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" ht="138.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>10</v>
       </c>
@@ -8682,7 +8682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="193.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" ht="138.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>10</v>
       </c>
@@ -8714,7 +8714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="304.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" ht="221.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>10</v>
       </c>
@@ -8746,7 +8746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="304.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" ht="193.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>10</v>
       </c>
@@ -8778,7 +8778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="180" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" ht="124.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>10</v>
       </c>
@@ -8810,7 +8810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="290.39999999999998" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" ht="221.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>10</v>
       </c>
@@ -8842,7 +8842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="276.60000000000002" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" ht="207.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>10</v>
       </c>
@@ -8874,7 +8874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="221.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" ht="152.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>10</v>
       </c>
@@ -8906,7 +8906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="276.60000000000002" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10" ht="180" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>10</v>
       </c>
@@ -8938,7 +8938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="262.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" ht="166.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>10</v>
       </c>
@@ -8970,7 +8970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="235.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" ht="166.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>10</v>
       </c>
@@ -9002,7 +9002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="359.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" ht="249" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>10</v>
       </c>
@@ -9034,7 +9034,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="318" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" ht="221.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>10</v>
       </c>
@@ -9066,7 +9066,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="304.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" ht="207.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>10</v>
       </c>
@@ -9098,7 +9098,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="318" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10" ht="249" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>10</v>
       </c>
@@ -9130,7 +9130,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="276.60000000000002" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10" ht="221.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>10</v>
       </c>
@@ -9162,7 +9162,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="345.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" ht="207.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>10</v>
       </c>
@@ -9194,7 +9194,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="262.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" ht="180" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>10</v>
       </c>
@@ -9226,7 +9226,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="235.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10" ht="166.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>10</v>
       </c>
@@ -9258,7 +9258,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" ht="400.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>10</v>
       </c>
